--- a/Pasta 5.xlsx
+++ b/Pasta 5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aluno\Documents\GitHub\Yasmim\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3ADB3297-0355-498E-97C7-D31A0372E3C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFA63179-6190-411A-8577-D6792479619D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14580" windowHeight="15585" xr2:uid="{F6527C89-FC57-4680-9F83-DE2F14772A23}"/>
+    <workbookView xWindow="2295" yWindow="2295" windowWidth="14340" windowHeight="11295" xr2:uid="{F6527C89-FC57-4680-9F83-DE2F14772A23}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -169,9 +169,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -182,6 +179,9 @@
     <xf numFmtId="44" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
@@ -512,10 +512,10 @@
       </c>
     </row>
     <row r="3" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="3"/>
+      <c r="B3" s="9"/>
       <c r="C3" s="2" t="s">
         <v>2</v>
       </c>
@@ -524,146 +524,148 @@
       </c>
     </row>
     <row r="5" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="5">
         <v>3</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="6">
         <v>4.5</v>
       </c>
-      <c r="D6" s="8">
-        <f>C6*B6</f>
+      <c r="D6" s="7">
+        <f t="shared" ref="D6:D12" si="0">C6*B6</f>
         <v>13.5</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="5">
         <v>2</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="6">
         <v>7</v>
       </c>
-      <c r="D7" s="8">
-        <f>C7*B7</f>
+      <c r="D7" s="7">
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="5">
         <v>1</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="6">
         <v>7.5</v>
       </c>
-      <c r="D8" s="8">
-        <f>C8*B8</f>
+      <c r="D8" s="7">
+        <f t="shared" si="0"/>
         <v>7.5</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="5">
         <v>2</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="6">
         <v>3.5</v>
       </c>
-      <c r="D9" s="8">
-        <f>C9*B9</f>
+      <c r="D9" s="7">
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="5">
         <v>3</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="6">
         <v>2</v>
       </c>
-      <c r="D10" s="8">
-        <f>C10*B10</f>
+      <c r="D10" s="7">
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="5">
         <v>2</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="6">
         <v>4</v>
       </c>
-      <c r="D11" s="8">
-        <f>C11*B11</f>
+      <c r="D11" s="7">
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="6">
+      <c r="B12" s="5">
         <v>2</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="6">
         <v>5</v>
       </c>
-      <c r="D12" s="8">
-        <f>C12*B12</f>
+      <c r="D12" s="7">
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D13" s="8">
+      <c r="D13" s="7">
         <f>D6+D7+D8+D9+D10+D11+D12</f>
         <v>66</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D14" s="9">
-        <v>6.6</v>
+      <c r="D14" s="8">
+        <f>D13*D3</f>
+        <v>6.6000000000000005</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D15" s="9">
+      <c r="D15" s="8">
+        <f>D13+D14</f>
         <v>72.599999999999994</v>
       </c>
     </row>
